--- a/26-09_September_Metadata.xlsx
+++ b/26-09_September_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F89D3E29-CFCC-483F-B19F-3B085EDBD8F8}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DEC936E-0433-411E-871E-FA1CBC360D49}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -2753,7 +2753,7 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" ht="180" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46140</v>
       </c>
@@ -3037,7 +3037,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
     </row>
-    <row r="29" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46170</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>325</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>16</v>
@@ -3756,7 +3756,7 @@
         <v>370</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>16</v>
@@ -3870,7 +3870,7 @@
       <c r="Q48" s="20"/>
       <c r="R48" s="20"/>
     </row>
-    <row r="49" spans="1:18" ht="180" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="165" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46266</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="Q49" s="20"/>
       <c r="R49" s="20"/>
     </row>
-    <row r="50" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46272</v>
       </c>

--- a/26-09_September_Metadata.xlsx
+++ b/26-09_September_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59C5F041-9DD1-494D-BE2D-DEF30571821A}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0730CCE-ABE9-44F1-BF5D-98FAC04941BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="435">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1320,6 +1320,30 @@
   </si>
   <si>
     <t>26-00041R3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gCkJ-uquIULnpHjSWqNWbWK-mGEC9kCe/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>building extraction; VHR remote sensing imagery; Transformer; skip connections; hybrid loss function</t>
+  </si>
+  <si>
+    <t>Building extraction from very-high-resolution (VHR) remote sensing imagery remains challenging because buildings exhibit large variations in scale and are often embedded in complex textured backgrounds. These characteristics increase visual similarity and spatial confusion between buildings and their surrounding environments, making it difficult for building extraction models to achieve both multi-scale representation and detail preservation. To address these issues, we propose the gated multi-scale interaction network (GMSINet), a U-shaped encoder–decoder framework with a hierarchical shifted-window self-attention Transformer backbone. To reduce feature redundancy, background-noise propagation, and unstable multi-scale fusion in skip connections, a gated multi-scale interaction module is designed. This module adaptively filters enhanced information through SimAM-based recalibration, multi-receptive-field interaction, and channel-wise gating, thereby improving feature fusion quality in the decoding stage without changing feature resolution. In addition, a hybrid loss function is introduced to balance pixel-level supervision stability and region-level structural consistency. Experiments on the Massachusetts, INRIA, and WHU building data sets show that GMSINet achieves intersection over union) scores of 74.50%, 77.35%, and 90.52%, respectively, outperforming the second-best models by 0.95%, 0.17%, and 0.25%, while maintaining stable overall accuracy and F1 score. These results demonstrate the effectiveness of GMSINet for building extraction from VHR remote sensing imagery.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00081R2</t>
+  </si>
+  <si>
+    <t>1: School of Surveying and Geo-Informatics, Shandong Jianzhu University 2: State Key Laboratory of Spatial Datum, Chinese Academy of Surveying and Mapping 3: Jinan Geotechnical Investigation and Surveying Institute</t>
+  </si>
+  <si>
+    <t>Yao, Guobiao 1, 2 ; Zhang, Zeyu 1 ; Wang, Qingdong 2 ; Zhang, Xianjun 3 ; Zhang, Li 2 ; </t>
+  </si>
+  <si>
+    <t>GMSINet for Building Extraction from Very-High-Resolution Remote Sensing Imagery</t>
+  </si>
+  <si>
+    <t>26-00081R2</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -4062,6 +4086,48 @@
       <c r="Q52" s="22"/>
       <c r="R52" s="21"/>
     </row>
+    <row r="53" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="O53" s="4"/>
+      <c r="P53" s="23"/>
+      <c r="Q53" s="23"/>
+      <c r="R53" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E12" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>
